--- a/backlog_tool/plantilla.xlsx
+++ b/backlog_tool/plantilla.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -140,8 +140,11 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -515,13 +518,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D28"/>
+  <dimension ref="B1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,6 +575,11 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
+          <t>Alternativas</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
           <t>Total Pares</t>
         </is>
       </c>
@@ -578,119 +587,156 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>68127 NE/RO SLI</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+          <t>68127</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>NE/RO SLI</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>3900</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>64197 NE SLI</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+          <t>64197</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>NE SLI</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>4100</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>65568 RO/HU SLI</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
+          <t>65568</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>RO/HU SLI</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>3300</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>(escribe modelo aquí)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>(modelo)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>(alternativa)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr"/>
-      <c r="C12" s="9" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="9" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="9" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="9" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="10" t="inlineStr"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="10" t="inlineStr"/>
-      <c r="C20" s="9" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="9" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="9" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="9" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="9" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="9" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="9" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="12">
-        <f>SUM(C8:C27)</f>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="13">
+        <f>SUM(D8:D27)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -702,164 +748,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>PLANTILLA DE BACKLOG (formato simple)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Cómo llenarla:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
+      <c r="A4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>1. Guarda este archivo con un nombre nuevo (ej: Backlog_Mayo.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>2. En la hoja 'Backlog':</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Celda C4: semana ISO de inicio (ej: 15)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Celda C5: semana ISO de fin (ej: 21)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Columna B: nombres de modelos (formato '12345 XX SLI')</t>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Columna B 'Modelo': SOLO el número de modelo (ej: 68127)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Columna C: total de pares por modelo para TODO el rango</t>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Columna C 'Alternativas': color/variante (ej: NE/RO SLI)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Columna D 'Total Pares': total para todo el rango</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>3. Guarda y corre:</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   python scripts/generar_propuesta_backlog.py --input Backlog_Mayo.xlsx</t>
-        </is>
-      </c>
+      <c r="A13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python backlog_tool/generar_propuesta.py --input Backlog_Mayo.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>El sistema distribuirá automáticamente:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Balanceando capacidad de robots (datos reales de Supabase)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Manteniendo mezcla baja (máx 5 modelos/semana)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Aislando modelos con robots restringidos</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Lotes contiguos (1-3 semanas por modelo según volumen)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Reglas del input:</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>• Modelos deben empezar con número de 4-6 dígitos</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>• Modelo: número de 4-6 dígitos (SIN texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>• Alternativas: texto libre (color, sufijo, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>• Total de pares: número entero</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>• Puedes agregar más filas, solo respeta el formato</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>• Modelos nuevos no en catálogo Supabase = tratados como 'sin catálogo'</t>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>• Modelos no encontrados en catálogo Supabase = tratados como 'sin catálogo'</t>
         </is>
       </c>
     </row>
